--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T18:57:20+00:00</t>
+    <t>2024-08-18T19:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T19:14:17+00:00</t>
+    <t>2024-10-17T13:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T13:36:11+00:00</t>
+    <t>2024-10-30T19:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T19:02:49+00:00</t>
+    <t>2024-11-07T20:59:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T20:59:16+00:00</t>
+    <t>2024-12-06T22:28:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -581,9 +581,6 @@
 An instance-order is an instantiation of a request or order and may be used to populate Medication Administration Record.  This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
-  </si>
-  <si>
-    <t>order</t>
   </si>
   <si>
     <t>The kind of medication order.</t>
@@ -3412,7 +3409,7 @@
         <v>21</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>21</v>
@@ -3430,10 +3427,10 @@
         <v>161</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3466,16 +3463,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
@@ -3483,10 +3480,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3512,13 +3509,13 @@
         <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3547,11 +3544,11 @@
         <v>173</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3568,7 +3565,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3586,13 +3583,13 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="AN15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
@@ -3600,10 +3597,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3629,10 +3626,10 @@
         <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3662,11 +3659,11 @@
         <v>161</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
       </c>
@@ -3683,7 +3680,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3698,16 +3695,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
@@ -3715,10 +3712,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3741,16 +3738,16 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3800,7 +3797,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3821,7 +3818,7 @@
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -3832,10 +3829,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3858,13 +3855,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3915,7 +3912,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3936,7 +3933,7 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -3947,10 +3944,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3976,13 +3973,13 @@
         <v>169</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4012,7 +4009,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4030,7 +4027,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>90</v>
@@ -4045,27 +4042,27 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4088,16 +4085,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4147,7 +4144,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>90</v>
@@ -4162,27 +4159,27 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4205,16 +4202,16 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4264,7 +4261,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4279,27 +4276,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>165</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4322,13 +4319,13 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4379,7 +4376,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4394,16 +4391,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
@@ -4411,10 +4408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4437,13 +4434,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4494,7 +4491,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4509,27 +4506,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4552,13 +4549,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4609,7 +4606,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4624,16 +4621,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>21</v>
@@ -4641,10 +4638,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4667,13 +4664,13 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4724,7 +4721,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4739,16 +4736,16 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>21</v>
@@ -4756,10 +4753,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4785,13 +4782,13 @@
         <v>169</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4820,11 +4817,11 @@
         <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4841,7 +4838,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4856,13 +4853,13 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
@@ -4873,10 +4870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4899,13 +4896,13 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4956,7 +4953,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4977,10 +4974,10 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
@@ -4988,10 +4985,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5017,13 +5014,13 @@
         <v>169</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5052,11 +5049,11 @@
         <v>173</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5073,7 +5070,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5088,27 +5085,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5131,16 +5128,16 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5190,7 +5187,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5205,16 +5202,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>165</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5222,10 +5219,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5248,13 +5245,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5305,7 +5302,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5320,13 +5317,13 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5337,10 +5334,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5366,10 +5363,10 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5420,7 +5417,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5441,7 +5438,7 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5452,10 +5449,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5478,13 +5475,13 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5535,7 +5532,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5550,13 +5547,13 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5567,10 +5564,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5596,14 +5593,14 @@
         <v>148</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5652,7 +5649,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5667,13 +5664,13 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
@@ -5684,10 +5681,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5713,13 +5710,13 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5748,11 +5745,11 @@
         <v>173</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>330</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5769,7 +5766,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5790,7 +5787,7 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -5801,10 +5798,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5827,13 +5824,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5884,7 +5881,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5899,13 +5896,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -5916,10 +5913,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5942,13 +5939,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5999,7 +5996,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6014,13 +6011,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -6031,10 +6028,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6057,16 +6054,16 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6116,7 +6113,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6131,13 +6128,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -6148,10 +6145,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6174,13 +6171,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6231,7 +6228,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6249,10 +6246,10 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6263,10 +6260,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6289,13 +6286,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6346,7 +6343,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6367,7 +6364,7 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6378,10 +6375,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6410,7 +6407,7 @@
         <v>137</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>139</v>
@@ -6463,7 +6460,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6484,7 +6481,7 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6495,14 +6492,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6524,10 +6521,10 @@
         <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>139</v>
@@ -6582,7 +6579,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6614,10 +6611,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6640,16 +6637,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6699,7 +6696,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6720,7 +6717,7 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6731,10 +6728,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6757,13 +6754,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6814,7 +6811,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6835,7 +6832,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6846,10 +6843,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6878,7 +6875,7 @@
         <v>137</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>139</v>
@@ -6931,7 +6928,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6952,7 +6949,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -6963,14 +6960,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6992,10 +6989,10 @@
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>139</v>
@@ -7050,7 +7047,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7082,10 +7079,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7108,13 +7105,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7165,7 +7162,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7186,7 +7183,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7197,10 +7194,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7223,13 +7220,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7280,7 +7277,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7301,7 +7298,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7312,10 +7309,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7338,13 +7335,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7395,7 +7392,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7416,7 +7413,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7427,10 +7424,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7453,19 +7450,19 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7514,7 +7511,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7532,10 +7529,10 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7546,10 +7543,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7572,16 +7569,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7631,7 +7628,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7649,24 +7646,24 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7689,13 +7686,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7746,7 +7743,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7764,24 +7761,24 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>414</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7804,16 +7801,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7863,7 +7860,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7881,10 +7878,10 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -7895,10 +7892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7921,13 +7918,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7978,7 +7975,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7999,10 +7996,10 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8010,10 +8007,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8036,13 +8033,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8093,7 +8090,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8111,10 +8108,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8125,10 +8122,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8151,13 +8148,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8208,7 +8205,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8229,7 +8226,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8240,10 +8237,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8272,7 +8269,7 @@
         <v>137</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>139</v>
@@ -8325,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8346,7 +8343,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8357,14 +8354,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8386,10 +8383,10 @@
         <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>139</v>
@@ -8444,7 +8441,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8476,10 +8473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8502,16 +8499,16 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8540,11 +8537,11 @@
         <v>173</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8561,7 +8558,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>90</v>
@@ -8579,24 +8576,24 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8622,10 +8619,10 @@
         <v>169</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8655,11 +8652,11 @@
         <v>173</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8676,7 +8673,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8694,24 +8691,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>450</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8734,13 +8731,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8791,7 +8788,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8806,13 +8803,13 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8823,14 +8820,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8849,16 +8846,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8908,7 +8905,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8929,7 +8926,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8940,10 +8937,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8966,16 +8963,16 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9025,7 +9022,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9040,13 +9037,13 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T22:28:12+00:00</t>
+    <t>2024-12-30T06:20:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T06:20:40+00:00</t>
+    <t>2025-01-13T15:35:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T15:35:56+00:00</t>
+    <t>2025-01-13T20:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T20:12:32+00:00</t>
+    <t>2025-01-30T04:55:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T04:55:08+00:00</t>
+    <t>2025-01-31T22:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T22:08:22+00:00</t>
+    <t>2025-02-01T06:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T06:47:49+00:00</t>
+    <t>2025-02-01T23:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:07:45+00:00</t>
+    <t>2025-02-01T23:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.4.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:40:00+00:00</t>
+    <t>2025-02-02T03:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivAltPepBackbonePrescription.xlsx
+++ b/StructureDefinition-HivAltPepBackbonePrescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-02T03:11:41+00:00</t>
+    <t>2025-03-10T17:41:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
